--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2237.</t>
+          <t>2354.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2354.</t>
+          <t>2722.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2722.</t>
+          <t>2637.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2637.</t>
+          <t>2671.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2671.</t>
+          <t>3055.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3055.</t>
+          <t>3078.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,49 +490,107 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>328.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 03:15 PM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2,81,43,000</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>28143000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>32</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3078.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>30-May-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>20-Jun-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2,70,53,943</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>27053943</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>193.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>17-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>18-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8,46,91,000</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>84691000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
         </is>
       </c>
     </row>

--- a/jammu_etenders.xlsx
+++ b/jammu_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>328.</t>
+          <t>2118.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,49 +548,223 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2902.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[BALANCE WORK FOR CONSTRUCTION OF NEW PAVILLION BUILDING AND OTHER ALLIED WORKS AT SUBASH STADIUM UDHMAPUR 2nd time ] [e nit 12 of 2026-27 dated 20.06.2026][2026_SPORT_313266_1]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>J and K State Sports Council||Sports Council Construction Div Jammu</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2,92,74,000</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>29274000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S9jWeTiz91AXTipQZplL8vg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2183.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[Dismantling and reconstruction of food store building at Hiranagar.] [e-NIT No.PWD/SE/KS/17 of 2026-27 Dated 22-06-2026][2026_PWDJK_313596_1]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,71,91,000</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>17191000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SV0hDtoZc4nr5h8jv1EdsVw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>32</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>193.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1994.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>25-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>17-Jul-2026 04:00 PM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>18-Jul-2026 12:00 PM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>PWD||CE RandB Jammu</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>8,46,91,000</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K5" t="n">
         <v>84691000</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3919.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>01-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[DESIGN, SUPPLY, INSTALLATION, TESTING, COMMISSIONING OF HVAC SYSTEM AT TEACHING HOSPITAL, GOVERNMENT MEDICAL COLLEGE DODA] [e- NIT No.MHCJ/Tech/e-NIT/2026-27/04 ][2026_PWDJK_311243_1]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PWD||CE MED Jammu||Mechanical Circle Jammu</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,97,94,781</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>49794781</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Slx9M53hmIEhkOsQJDIct2w%3D%3D</t>
         </is>
       </c>
     </row>
